--- a/Aps-BootUI/src/main/resources/excelTemplateModel/gdyy/钢带压延排程结果信息en.xlsx
+++ b/Aps-BootUI/src/main/resources/excelTemplateModel/gdyy/钢带压延排程结果信息en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\Aps\Aps-BootUI\src\main\resources\excelTemplateModel\gdyy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DC-APS\Aps-BootUI\src\main\resources\excelTemplateModel\gdyy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6F3EC8-F878-4E24-B47D-6BF5CB5F804A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D678D2-53DD-4054-AEDB-24FD9E94887F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="钢带压延排程结果" sheetId="2" r:id="rId1"/>
@@ -20,26 +20,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>基本信息</t>
   </si>
   <si>
-    <t>中班计划（16:00-24:00）</t>
-  </si>
-  <si>
-    <t>夜班计划（0:00-8:00）</t>
-  </si>
-  <si>
     <t>白班计划（8:00-16:00）</t>
   </si>
   <si>
     <t>钢压大卷代号</t>
   </si>
   <si>
-    <t>中班备注</t>
-  </si>
-  <si>
     <t>夜班备注</t>
   </si>
   <si>
@@ -54,47 +45,59 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>中班计划量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中班支领量(米)</t>
+    <t>白班计划量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白班支领量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日用参考(米)（不生效）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注(不生效)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>白班无库存计划量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜班计划（19:00-7:00）</t>
+  </si>
+  <si>
+    <t>夜班计划（7:00-19:00）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>夜班计划量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜班无库存计划量(米)</t>
   </si>
   <si>
     <t>夜班支领量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>白班计划量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>白班支领量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日用参考(米)（不生效）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注(不生效)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中班无库存计划量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>夜班无库存计划量(米)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>白班无库存计划量(米)</t>
+  </si>
+  <si>
+    <t>早班计划量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班无库存计划量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班支领量(米)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班备注</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生产线</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -184,17 +187,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
@@ -206,8 +209,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -513,114 +519,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="3" width="16.81640625" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
-    <col min="6" max="6" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7265625" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" customWidth="1"/>
-    <col min="9" max="9" width="14.7265625" customWidth="1"/>
-    <col min="10" max="10" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7265625" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" customWidth="1"/>
-    <col min="13" max="13" width="14.7265625" customWidth="1"/>
-    <col min="14" max="14" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7265625" customWidth="1"/>
-    <col min="16" max="16" width="10.36328125" customWidth="1"/>
-    <col min="17" max="17" width="9.1796875" customWidth="1"/>
+    <col min="1" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.77734375" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" customWidth="1"/>
+    <col min="7" max="7" width="22.21875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="11.21875" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" customWidth="1"/>
+    <col min="11" max="11" width="22.21875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" customWidth="1"/>
+    <col min="14" max="14" width="14.77734375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="22.21875" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="14.77734375" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
-      <c r="I1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="K1" s="7"/>
       <c r="L1" s="7"/>
-      <c r="M1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7" t="s">
+        <v>1</v>
+      </c>
       <c r="O1" s="7"/>
       <c r="P1" s="7"/>
-      <c r="Q1" s="4"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="4"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="1" customFormat="1" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="R2" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
